--- a/jpcore-r4/release/v1.2.0/ValueSet-jp-dental-surfacebodystructure-vs.xlsx
+++ b/jpcore-r4/release/v1.2.0/ValueSet-jp-dental-surfacebodystructure-vs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalSurfaceBodyStructure_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalSurfaceBodyStructure_VS</t>
   </si>
   <si>
     <t>Version</t>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>JP Core Dental BodyStructure ValueSet</t>
+    <t>JP Core Dental SurfaceBodyStructure ValueSet</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-12</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>
